--- a/results/job_matches_2026-10-07.xlsx
+++ b/results/job_matches_2026-10-07.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -666,17 +666,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NodeJS/AWS Fullstack developer - Software Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -684,7 +684,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,32 +694,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9b6e62814d5305</t>
+          <t>https://www.indeed.com/viewjob?jk=cc5341b3eae13016</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Node js/AWS fullstack developerSoftware Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>mPulse</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20.8</v>
+        <v>19.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -729,19 +729,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262e6fd34c0f8ab5</t>
+          <t>https://www.indeed.com/viewjob?jk=341da7dee83bcecc</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>mPulse</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -750,11 +750,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>20.8</v>
+        <v>19.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,32 +764,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc5341b3eae13016</t>
+          <t>https://www.indeed.com/viewjob?jk=958b77c45e6daea7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>mPulse</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,207 +799,207 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341da7dee83bcecc</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf6cb804310788f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Vulnerability Management Engineer (Onsite Hybrid)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>mPulse</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, EMR, IAM, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958b77c45e6daea7</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac0a80ae78e8a3b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Enterprise Architect-5</t>
+          <t>GCP Data Engineer – Remote</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>YT Global Network</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f4e7353d156d21</t>
+          <t>https://www.indeed.com/viewjob?jk=4b02a541e66f4c5b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud Vulnerability Management Engineer (Onsite Hybrid)</t>
+          <t>Sr Software Engineer - Digital Banking</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, IAM, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ac0a80ae78e8a3b</t>
+          <t>https://www.indeed.com/viewjob?jk=acb73e15b88b41b2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer, Data - FreeWheel</t>
+          <t>AWS DevOps Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Hadoop, HDFS, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51fb9c7f9097d165</t>
+          <t>https://www.indeed.com/viewjob?jk=20ae1a526db03909</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GCP Data Engineer – Remote</t>
+          <t>Senior AI Ops / DevOps Engineer (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>YT Global Network</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Hive, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b02a541e66f4c5b</t>
+          <t>https://www.indeed.com/viewjob?jk=6415d34be34565d8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,32 +1009,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=850f4c0879ad3a62</t>
+          <t>https://www.indeed.com/viewjob?jk=ac695015f6e52803</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Digital Banking</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1044,59 +1044,59 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb73e15b88b41b2</t>
+          <t>https://www.indeed.com/viewjob?jk=a88c40e681df4e1a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior AI Ops / DevOps Engineer (FTE / Hybrid)</t>
+          <t>Senior Machine Learning Engineer, Fraud Risk Modeling</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6415d34be34565d8</t>
+          <t>https://www.indeed.com/viewjob?jk=0c1b0bc837735bcf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Kroll Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, NoSQL, dbt</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,32 +1114,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3904d0205e58da2c</t>
+          <t>https://www.indeed.com/viewjob?jk=78b96535deace3b6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kroll Inc.</t>
+          <t>Howard Hughes Medical Institute</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,59 +1149,59 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78b96535deace3b6</t>
+          <t>https://www.indeed.com/viewjob?jk=97c5e1818487b920</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Data Engineer (Platform)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04b6ea3bc33b1453</t>
+          <t>https://www.indeed.com/viewjob?jk=75ceb496aa16205b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer (Platform)</t>
+          <t>Data Engineer - ONSITE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Network Distribution</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,24 +1219,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75ceb496aa16205b</t>
+          <t>https://www.indeed.com/viewjob?jk=271ae7d8ee6706bd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer - ONSITE</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Network Distribution</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1254,14 +1254,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271ae7d8ee6706bd</t>
+          <t>https://www.indeed.com/viewjob?jk=7e6a45e7ed84165b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Angular Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1289,32 +1289,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e6a45e7ed84165b</t>
+          <t>https://www.indeed.com/viewjob?jk=934be651d2822067</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, Scala, PostgreSQL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934be651d2822067</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2ab2b60d846cd6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, Scala, PostgreSQL, ELT, dbt, CI/CD</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1359,14 +1359,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2ab2b60d846cd6</t>
+          <t>https://www.indeed.com/viewjob?jk=aac1512204e679c4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,24 +1394,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aac1512204e679c4</t>
+          <t>https://www.indeed.com/viewjob?jk=aea92000540cf9d5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Sr Engineer, IT Machine Learning</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, Scala, Oracle, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1429,32 +1429,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aea92000540cf9d5</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9e361c44f6f503</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Engineer, IT Machine Learning</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>NAC Architecture</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Oracle, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab9e361c44f6f503</t>
+          <t>https://www.indeed.com/viewjob?jk=de63d204e832110a</t>
         </is>
       </c>
     </row>
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>NAC Architecture</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Spokane, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1499,24 +1499,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b7784fe0428d5f</t>
+          <t>https://www.indeed.com/viewjob?jk=876322e831ec8eca</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer – Physical AI Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>NAC Architecture</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1534,24 +1534,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8048f9d73fd7da7</t>
+          <t>https://www.indeed.com/viewjob?jk=7c07ba22730cc31c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ProMach</t>
+          <t>NAC Architecture</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1569,24 +1569,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c9f802c8d368c6</t>
+          <t>https://www.indeed.com/viewjob?jk=0d993410e2b916af</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1604,102 +1604,102 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f35bd1de3b8b37e</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b7784fe0428d5f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer-4</t>
+          <t>Data Engineer – Physical AI Platform</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7d0c3f29b8874fb</t>
+          <t>https://www.indeed.com/viewjob?jk=a8048f9d73fd7da7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>iClassPro, Inc.</t>
+          <t>ProMach</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, RDS, Scala, ETL, ELT, dbt</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=579a554b68cd573e</t>
+          <t>https://www.indeed.com/viewjob?jk=66c9f802c8d368c6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Credit Union of Texas</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1709,24 +1709,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933f7b241bea8b88</t>
+          <t>https://www.indeed.com/viewjob?jk=0f35bd1de3b8b37e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Back-End Developer</t>
+          <t>Analytics Engineer II, Marketing Technology - Remote</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>OneDigital</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1734,34 +1734,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Blob Storage, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d422fc46951e5afd</t>
+          <t>https://www.indeed.com/viewjob?jk=238a27c5210ae789</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud Engineer-API -Global Industrial</t>
+          <t>Software Engineer - Data Architecture &amp; Platform Engineering</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>News Corp</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1769,104 +1769,104 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1626850211bd78e</t>
+          <t>https://www.indeed.com/viewjob?jk=923379e0dc0b8dde</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer-4</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Easterseals Southern California</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07870ee9c10ac5c8</t>
+          <t>https://www.indeed.com/viewjob?jk=c7d0c3f29b8874fb</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Credit Union of Texas</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Allen, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b788dde189e4cc1</t>
+          <t>https://www.indeed.com/viewjob?jk=933f7b241bea8b88</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Easterseals Southern California</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1884,24 +1884,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be020efc616ae06a</t>
+          <t>https://www.indeed.com/viewjob?jk=07870ee9c10ac5c8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Architect – GCP / Generative AI</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1919,24 +1919,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26593bdfa803230a</t>
+          <t>https://www.indeed.com/viewjob?jk=be020efc616ae06a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Senior Agentic Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Harris Computer</t>
+          <t>Farther</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Azure, GCP, Vertex AI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1954,24 +1954,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=274f51e93c4990cb</t>
+          <t>https://www.indeed.com/viewjob?jk=c814d297706f8656</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Agentic Engineer</t>
+          <t>Sr. Information Security Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Farther</t>
+          <t>reveleer</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1979,34 +1979,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Azure, GCP, Vertex AI</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Databricks, GCP, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c814d297706f8656</t>
+          <t>https://www.indeed.com/viewjob?jk=30bee6defc91ca2b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Agentic Engineer</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Farther</t>
+          <t>Harris Computer</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Azure, GCP, Vertex AI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2024,19 +2024,19 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a058514bb5e480b</t>
+          <t>https://www.indeed.com/viewjob?jk=274f51e93c4990cb</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer - Advanced Analytics</t>
+          <t>Senior Software Engineer – Backend</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2049,34 +2049,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, PostgreSQL, Data Modeling, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44ef5d52f3729890</t>
+          <t>https://www.indeed.com/viewjob?jk=ff1e374638f96eca</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Backend</t>
+          <t>Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tempus</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2094,24 +2094,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff1e374638f96eca</t>
+          <t>https://www.indeed.com/viewjob?jk=5131e2f85865e971</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineers</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Pacific Gas and Electric</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2119,29 +2119,29 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Hive, Spark, Kafka, NoSQL, Data Modeling, ETL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4c126f4e3cc33b7</t>
+          <t>https://www.indeed.com/viewjob?jk=7cc4e057f32c8e6e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Pacific Gas and Electric</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Spark, PySpark, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,24 +2164,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8456a013be9abe6d</t>
+          <t>https://www.indeed.com/viewjob?jk=e4c126f4e3cc33b7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer - Associate</t>
+          <t>Professional Services Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Richmond</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Dataflow, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2199,24 +2199,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47786603c2f15c79</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f07433764ff47c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Allied Benefit Systems</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2224,34 +2224,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2168430383941cce</t>
+          <t>https://www.indeed.com/viewjob?jk=8456a013be9abe6d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>AI Solutions Engineer - Associate</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Federal Reserve Bank of Richmond</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06a412cb9f758689</t>
+          <t>https://www.indeed.com/viewjob?jk=47786603c2f15c79</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Platform &amp; DevSecOps Delivery Architect</t>
+          <t>2027 Capital Markets, Quantitative Technology Services Summer, Raleigh</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Harris Computer</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2304,24 +2304,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cfe33f29178a80c</t>
+          <t>https://www.indeed.com/viewjob?jk=ea97b81f8a8fbea5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Software Engineer Analyst</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, ETL, Talend, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2339,24 +2339,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d32bc60368c3a448</t>
+          <t>https://www.indeed.com/viewjob?jk=15d208d296c27320</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr AI/Data Science Engineer</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2374,24 +2374,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96bdba5085886da3</t>
+          <t>https://www.indeed.com/viewjob?jk=06a412cb9f758689</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Advanced Software Engineer</t>
+          <t>Software Engineer III - Backend</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2399,34 +2399,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, Vertex AI, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbab632d0bb04999</t>
+          <t>https://www.indeed.com/viewjob?jk=3bfe9ad476bd328d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Meetic</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2444,24 +2444,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcdac1dc01d8884d</t>
+          <t>https://www.indeed.com/viewjob?jk=d57923c372a91491</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Professional Services Engineer</t>
+          <t>Sr AI/Data Science Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Dataflow, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2479,67 +2479,67 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f07433764ff47c</t>
+          <t>https://www.indeed.com/viewjob?jk=96bdba5085886da3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - Card Tech</t>
+          <t>Software Engineer III, Backend</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Tinder</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=854d296ae3e1537f</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd1157f032a62ba</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Software Engineer III, Backend</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>North South Consulting Group</t>
+          <t>Meetic</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, ECS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33388762be2726a2</t>
+          <t>https://www.indeed.com/viewjob?jk=bcdac1dc01d8884d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, ETL, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2584,24 +2584,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31614612c22a3bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=d32bc60368c3a448</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Wireless Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>DMI</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Crownsville, MD, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2619,19 +2619,19 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42345033b70a0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=64fcbfb44e8f3307</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>North South Consulting Group</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2654,24 +2654,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b2eaf336ce0560</t>
+          <t>https://www.indeed.com/viewjob?jk=33388762be2726a2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Oracle Database Architect</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Woodland Hills, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, Data Modeling, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2689,24 +2689,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7ff4c841a1ca7d4</t>
+          <t>https://www.indeed.com/viewjob?jk=31614612c22a3bf8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Erwin Data Modeler</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tekcogno</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Scala, Snowflake, Oracle, SQL Server, MongoDB, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2724,24 +2724,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89810a7e8484847e</t>
+          <t>https://www.indeed.com/viewjob?jk=d42345033b70a0ad</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DBT/Python/Airflow Developer</t>
+          <t>Infrastructure Engineers</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2749,34 +2749,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, S3, RDS, Hadoop, Hive, Sqoop, HBase, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551ec71ed16874e7</t>
+          <t>https://www.indeed.com/viewjob?jk=6dcf5d44e6e794f0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Test Automation Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>World Emblem International</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, SQL Server, Dimensional Modeling, Star Schema, Dimension Tables, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2794,24 +2794,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb03498bcaeb2d4</t>
+          <t>https://www.indeed.com/viewjob?jk=64b2eaf336ce0560</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Analytics Engineer, Associate</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>World Emblem International</t>
+          <t>TPG</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2819,34 +2819,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, SQL Server, Dimensional Modeling, Star Schema, Dimension Tables, ETL, ELT</t>
+          <t>AWS, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0020052b83f9ef57</t>
+          <t>https://www.indeed.com/viewjob?jk=a6e6546ed6025d10</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Erwin Data Modeler</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>World Emblem International</t>
+          <t>Tekcogno</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Norcross, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, SQL Server, Dimensional Modeling, Star Schema, Dimension Tables, ETL, ELT</t>
+          <t>RDS, Hadoop, Scala, Snowflake, Oracle, SQL Server, MongoDB, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2864,67 +2864,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=767b9e8e13621baf</t>
+          <t>https://www.indeed.com/viewjob?jk=89810a7e8484847e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform Engineering</t>
+          <t>DBT/Python/Airflow Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77e2e5fec6bdd9d</t>
+          <t>https://www.indeed.com/viewjob?jk=551ec71ed16874e7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Enterprise Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>World Emblem International</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>RDS, Azure, Data Factory, Dataflow, SQL Server, Dimensional Modeling, Star Schema, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2934,32 +2934,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e4f2633f539c6b2</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb03498bcaeb2d4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Digital Scientist</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Church &amp; Dwight Co.</t>
+          <t>World Emblem International</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Power BI, Tableau, Git, Python, Scala, R</t>
+          <t>RDS, Azure, Data Factory, Dataflow, SQL Server, Dimensional Modeling, Star Schema, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2969,32 +2969,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe49970cad773e80</t>
+          <t>https://www.indeed.com/viewjob?jk=0020052b83f9ef57</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full-Stack Developer - Angular Focus</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Imperial Health Holdings</t>
+          <t>World Emblem International</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Norcross, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, SQL Server, PostgreSQL, ETL, CI/CD, Docker, Git</t>
+          <t>RDS, Azure, Data Factory, Dataflow, SQL Server, Dimensional Modeling, Star Schema, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3004,67 +3004,67 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca22063859741953</t>
+          <t>https://www.indeed.com/viewjob?jk=767b9e8e13621baf</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Fullstack Developer</t>
+          <t>Full-stack Engineer 4 (AWS, Java/ Python, Database, Go)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6372ad68f53bdf20</t>
+          <t>https://www.indeed.com/viewjob?jk=35ba6de05ae13211</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Full Stack Software Engineer 4 - Go, Python, Java, AWS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Innovate Tech IT LLC</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Sheridan, WY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3074,32 +3074,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e9b73c6f8692132</t>
+          <t>https://www.indeed.com/viewjob?jk=42b5b5030b63cf61</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - NC - Mandarin Speaking (Full-time, Exempt)</t>
+          <t>Full-stack Engineer 4 (Java, Python, AWS)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3109,24 +3109,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d98c4c1704c4e527</t>
+          <t>https://www.indeed.com/viewjob?jk=00983a19f7d4e161</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - CA - Mandarin Speaking</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Aventura, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3144,24 +3144,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc57e420a23e41b3</t>
+          <t>https://www.indeed.com/viewjob?jk=c493980a69f74556</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Senior Software Engineer, Platform Engineering</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, IAM, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3179,24 +3179,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c1901ef9cd7bdba</t>
+          <t>https://www.indeed.com/viewjob?jk=b77e2e5fec6bdd9d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Novacis Digital</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3204,34 +3204,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb729860cdaaf66</t>
+          <t>https://www.indeed.com/viewjob?jk=2e4f2633f539c6b2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Ericsson</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Aventura, FL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3239,34 +3239,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c493980a69f74556</t>
+          <t>https://www.indeed.com/viewjob?jk=e3250fba091a2092</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Engineer III, Business Intelligence</t>
+          <t>Software Engineer - Mid Level</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Mobis Parts America, LLC.</t>
+          <t>Cenergistic</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Fountain Valley, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, Athena, S3, SQS, ECS, Scala, PostgreSQL, DynamoDB, Docker, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3284,7 +3284,252 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a84d75c098494a33</t>
+          <t>https://www.indeed.com/viewjob?jk=a06fdb5232c62474</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Engineer – Apply For CircleCard</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Brooklyn Park, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47ca3963cee3be6c</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Sr. Fullstack Developer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ExxonMobil</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6372ad68f53bdf20</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Innovate Tech IT LLC</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Sheridan, WY, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e9b73c6f8692132</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>DevOps/SRE Engineer - NC - Mandarin Speaking (Full-time, Exempt)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Cwill</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d98c4c1704c4e527</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>DevOps/SRE Engineer - CA - Mandarin Speaking</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Cwill</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>City of Industry, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc57e420a23e41b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Cwill</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c1901ef9cd7bdba</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Novacis Digital</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Rockville, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>IAM, Azure, Data Factory, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ddb729860cdaaf66</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-10-07.xlsx
+++ b/results/job_matches_2026-10-07.xlsx
@@ -1191,17 +1191,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer - ONSITE</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Network Distribution</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, RDS, Cloud Storage, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1219,14 +1219,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=271ae7d8ee6706bd</t>
+          <t>https://www.indeed.com/viewjob?jk=7e6a45e7ed84165b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Angular Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1254,32 +1254,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e6a45e7ed84165b</t>
+          <t>https://www.indeed.com/viewjob?jk=934be651d2822067</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, Scala, PostgreSQL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1289,24 +1289,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934be651d2822067</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2ab2b60d846cd6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, Scala, PostgreSQL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1324,24 +1324,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2ab2b60d846cd6</t>
+          <t>https://www.indeed.com/viewjob?jk=aea92000540cf9d5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Sr Engineer, IT Machine Learning</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Azure, Databricks, Scala, Oracle, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1359,14 +1359,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aac1512204e679c4</t>
+          <t>https://www.indeed.com/viewjob?jk=ab9e361c44f6f503</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,32 +1394,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aea92000540cf9d5</t>
+          <t>https://www.indeed.com/viewjob?jk=aac1512204e679c4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Engineer, IT Machine Learning</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>NAC Architecture</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Oracle, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab9e361c44f6f503</t>
+          <t>https://www.indeed.com/viewjob?jk=de63d204e832110a</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Spokane, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de63d204e832110a</t>
+          <t>https://www.indeed.com/viewjob?jk=876322e831ec8eca</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spokane, WA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=876322e831ec8eca</t>
+          <t>https://www.indeed.com/viewjob?jk=7c07ba22730cc31c</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c07ba22730cc31c</t>
+          <t>https://www.indeed.com/viewjob?jk=0d993410e2b916af</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NAC Architecture</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1569,24 +1569,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d993410e2b916af</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b7784fe0428d5f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GenAI Engineer / Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1604,24 +1604,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b7784fe0428d5f</t>
+          <t>https://www.indeed.com/viewjob?jk=073e98661976c07a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer – Physical AI Platform</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>ProMach</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, Azure, Scala, DynamoDB, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1639,24 +1639,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8048f9d73fd7da7</t>
+          <t>https://www.indeed.com/viewjob?jk=66c9f802c8d368c6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ProMach</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1674,24 +1674,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c9f802c8d368c6</t>
+          <t>https://www.indeed.com/viewjob?jk=0f35bd1de3b8b37e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Site Reliability Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f35bd1de3b8b37e</t>
+          <t>https://www.indeed.com/viewjob?jk=26cf82ccf38514ed</t>
         </is>
       </c>
     </row>
@@ -1891,17 +1891,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>Senior Security Platform Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1909,34 +1909,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be020efc616ae06a</t>
+          <t>https://www.indeed.com/viewjob?jk=f48fee844cd0c55d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Agentic Engineer</t>
+          <t>Sr. Information Security Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Farther</t>
+          <t>reveleer</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1944,34 +1944,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, RDS, Azure, GCP, Vertex AI</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Databricks, GCP, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c814d297706f8656</t>
+          <t>https://www.indeed.com/viewjob?jk=30bee6defc91ca2b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Information Security Engineer</t>
+          <t>District Integration &amp; Support Engineer (Systems Engineer I) - 61161120</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>reveleer</t>
+          <t>State of South Carolina</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1979,34 +1979,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Databricks, GCP, MLOps, MLflow</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Talend, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30bee6defc91ca2b</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ffc90f30b5ea7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Harris Computer</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2024,24 +2024,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=274f51e93c4990cb</t>
+          <t>https://www.indeed.com/viewjob?jk=be020efc616ae06a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Backend</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Harris Computer</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2059,24 +2059,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff1e374638f96eca</t>
+          <t>https://www.indeed.com/viewjob?jk=274f51e93c4990cb</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Visualization Engineer</t>
+          <t>Senior Software Engineer – Backend</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tempus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, dbt, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2094,59 +2094,59 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5131e2f85865e971</t>
+          <t>https://www.indeed.com/viewjob?jk=ff1e374638f96eca</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineers</t>
+          <t>Data Visualization Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Tempus</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, Spark, Kafka, NoSQL, Data Modeling, ETL, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cc4e057f32c8e6e</t>
+          <t>https://www.indeed.com/viewjob?jk=5131e2f85865e971</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Professional Services Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pacific Gas and Electric</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Dataflow, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,24 +2164,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4c126f4e3cc33b7</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f07433764ff47c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Professional Services Engineer</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Dataflow, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2199,24 +2199,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f07433764ff47c</t>
+          <t>https://www.indeed.com/viewjob?jk=8456a013be9abe6d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>AI Solutions Engineer - Associate</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Federal Reserve Bank of Richmond</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2234,24 +2234,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8456a013be9abe6d</t>
+          <t>https://www.indeed.com/viewjob?jk=47786603c2f15c79</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer - Associate</t>
+          <t>Senior Software Engineer- Enterprise Platforms</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Richmond</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2259,34 +2259,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47786603c2f15c79</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1c6131bc8b3c29</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2027 Capital Markets, Quantitative Technology Services Summer, Raleigh</t>
+          <t>Senior Architect - Data &amp; Analytics COE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RBC</t>
+          <t>United Nations Federal Credit Union</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2304,24 +2304,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea97b81f8a8fbea5</t>
+          <t>https://www.indeed.com/viewjob?jk=4543534bd5d880f4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer Analyst</t>
+          <t>2027 Capital Markets, Quantitative Technology Services Summer, Raleigh</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2339,24 +2339,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15d208d296c27320</t>
+          <t>https://www.indeed.com/viewjob?jk=ea97b81f8a8fbea5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Full Stack Software Engineer Analyst</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2374,24 +2374,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06a412cb9f758689</t>
+          <t>https://www.indeed.com/viewjob?jk=15d208d296c27320</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer III - Backend</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2409,24 +2409,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bfe9ad476bd328d</t>
+          <t>https://www.indeed.com/viewjob?jk=d57923c372a91491</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr AI/Data Science Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>MiniMed</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Northridge, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2444,24 +2444,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57923c372a91491</t>
+          <t>https://www.indeed.com/viewjob?jk=96bdba5085886da3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr AI/Data Science Engineer</t>
+          <t>Software Engineer III - Backend</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96bdba5085886da3</t>
+          <t>https://www.indeed.com/viewjob?jk=3bfe9ad476bd328d</t>
         </is>
       </c>
     </row>
@@ -2521,17 +2521,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Meetic</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2549,24 +2549,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcdac1dc01d8884d</t>
+          <t>https://www.indeed.com/viewjob?jk=06a412cb9f758689</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III, Backend</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Meetic</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, ETL, Talend, CI/CD</t>
+          <t>AWS, ECS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d32bc60368c3a448</t>
+          <t>https://www.indeed.com/viewjob?jk=bcdac1dc01d8884d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Wireless Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DMI</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Crownsville, MD, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, ETL, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2619,24 +2619,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fcbfb44e8f3307</t>
+          <t>https://www.indeed.com/viewjob?jk=d32bc60368c3a448</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Wireless Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>North South Consulting Group</t>
+          <t>DMI</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Crownsville, MD, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2654,24 +2654,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33388762be2726a2</t>
+          <t>https://www.indeed.com/viewjob?jk=64fcbfb44e8f3307</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Nuuly</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Zookeeper, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2689,24 +2689,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31614612c22a3bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=7c18e77b373c042e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>North South Consulting Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2724,24 +2724,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42345033b70a0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=33388762be2726a2</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Infrastructure Engineers</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2749,34 +2749,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Hadoop, Hive, Sqoop, HBase, Kafka, Oracle, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dcf5d44e6e794f0</t>
+          <t>https://www.indeed.com/viewjob?jk=31614612c22a3bf8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2794,24 +2794,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b2eaf336ce0560</t>
+          <t>https://www.indeed.com/viewjob?jk=d42345033b70a0ad</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Associate</t>
+          <t>Full-Stack Software Engineer – Azure Practitioner</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>TPG</t>
+          <t>KCI Technologies</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2819,34 +2819,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6e6546ed6025d10</t>
+          <t>https://www.indeed.com/viewjob?jk=d231129436df5d79</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Erwin Data Modeler</t>
+          <t>Analytics Engineer, Associate</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tekcogno</t>
+          <t>TPG</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2854,34 +2854,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Scala, Snowflake, Oracle, SQL Server, MongoDB, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89810a7e8484847e</t>
+          <t>https://www.indeed.com/viewjob?jk=a6e6546ed6025d10</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DBT/Python/Airflow Developer</t>
+          <t>Erwin Data Modeler</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Tekcogno</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2889,34 +2889,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>RDS, Hadoop, Scala, Snowflake, Oracle, SQL Server, MongoDB, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551ec71ed16874e7</t>
+          <t>https://www.indeed.com/viewjob?jk=89810a7e8484847e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>DBT/Python/Airflow Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>World Emblem International</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2924,17 +2924,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, SQL Server, Dimensional Modeling, Star Schema, Dimension Tables, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb03498bcaeb2d4</t>
+          <t>https://www.indeed.com/viewjob?jk=551ec71ed16874e7</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0020052b83f9ef57</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb03498bcaeb2d4</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Norcross, GA, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3004,24 +3004,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=767b9e8e13621baf</t>
+          <t>https://www.indeed.com/viewjob?jk=0020052b83f9ef57</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (AWS, Java/ Python, Database, Go)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>World Emblem International</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Norcross, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Dataflow, SQL Server, Dimensional Modeling, Star Schema, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3039,14 +3039,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35ba6de05ae13211</t>
+          <t>https://www.indeed.com/viewjob?jk=767b9e8e13621baf</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer 4 - Go, Python, Java, AWS</t>
+          <t>Full-stack Engineer 4 (AWS, Java/ Python, Database, Go)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3074,14 +3074,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b5b5030b63cf61</t>
+          <t>https://www.indeed.com/viewjob?jk=35ba6de05ae13211</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Java, Python, AWS)</t>
+          <t>Full Stack Software Engineer 4 - Go, Python, Java, AWS</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3109,32 +3109,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00983a19f7d4e161</t>
+          <t>https://www.indeed.com/viewjob?jk=42b5b5030b63cf61</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full-stack Engineer 4 (Java, Python, AWS)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Aventura, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3144,24 +3144,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c493980a69f74556</t>
+          <t>https://www.indeed.com/viewjob?jk=00983a19f7d4e161</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform Engineering</t>
+          <t>Clinician-Developer: Cloud &amp; Integrations</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Charleston Children’s Therapy Center</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3169,34 +3169,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, Docker, AKS</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77e2e5fec6bdd9d</t>
+          <t>https://www.indeed.com/viewjob?jk=bf03acdee6bfb411</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Enterprise Data Engineer</t>
+          <t>Data Analytics Engineer (In Person)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>Westchester Medical Center Health Network</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>Valhalla, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3204,34 +3204,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e4f2633f539c6b2</t>
+          <t>https://www.indeed.com/viewjob?jk=6442e1547a870e80</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ericsson</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Aventura, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3239,34 +3239,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ELT, dbt, Git</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3250fba091a2092</t>
+          <t>https://www.indeed.com/viewjob?jk=c493980a69f74556</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer - Mid Level</t>
+          <t>Senior Software Engineer, Platform Engineering</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cenergistic</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, SQS, ECS, Scala, PostgreSQL, DynamoDB, Docker, Git</t>
+          <t>AWS, IAM, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3284,24 +3284,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a06fdb5232c62474</t>
+          <t>https://www.indeed.com/viewjob?jk=b77e2e5fec6bdd9d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Engineer – Apply For CircleCard</t>
+          <t>Enterprise Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Shelter Insurance</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Columbia, MO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3309,34 +3309,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ca3963cee3be6c</t>
+          <t>https://www.indeed.com/viewjob?jk=2e4f2633f539c6b2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Fullstack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Ericsson</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3344,17 +3344,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, ETL, ELT, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, Star Schema, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6372ad68f53bdf20</t>
+          <t>https://www.indeed.com/viewjob?jk=e3250fba091a2092</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-10-07.xlsx
+++ b/results/job_matches_2026-10-07.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,20 +531,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KLS Martin Group</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>26.4</v>
+        <v>23.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, GCP, BigQuery</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -554,32 +554,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d004bc892c60770</t>
+          <t>https://www.indeed.com/viewjob?jk=e99bcc3745577f44</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nixon Web Technology</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>25.7</v>
+        <v>20.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ec453d2d16d9041</t>
+          <t>https://www.indeed.com/viewjob?jk=cc5341b3eae13016</t>
         </is>
       </c>
     </row>
@@ -601,90 +601,90 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>iSynergy Information Technologies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Texas City, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>23.6</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, EMR, Redshift, S3, Azure, Data Factory, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99bcc3745577f44</t>
+          <t>https://www.indeed.com/viewjob?jk=42b30786a83d421a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Hadoop Solutions Developer</t>
+          <t>AWS Data Engineer (AWS Glue | DMS | CDC | Kafka)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>TEQDATA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.8</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Glue, SQS, SNS, IAM, Spark, PySpark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c64452ea9ee84058</t>
+          <t>https://www.indeed.com/viewjob?jk=8e22512bfc4565e4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>mPulse</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.8</v>
+        <v>19.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Spark Streaming, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc5341b3eae13016</t>
+          <t>https://www.indeed.com/viewjob?jk=341da7dee83bcecc</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -729,19 +729,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341da7dee83bcecc</t>
+          <t>https://www.indeed.com/viewjob?jk=958b77c45e6daea7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>mPulse</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -750,11 +750,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Scala, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -764,19 +764,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=958b77c45e6daea7</t>
+          <t>https://www.indeed.com/viewjob?jk=9cf6cb804310788f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>GCP Data Engineer – Remote</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>YT Global Network</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -785,11 +785,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Hive, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -799,137 +799,137 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cf6cb804310788f</t>
+          <t>https://www.indeed.com/viewjob?jk=4b02a541e66f4c5b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cloud Vulnerability Management Engineer (Onsite Hybrid)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GroundWork Renewables, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, IAM, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ac0a80ae78e8a3b</t>
+          <t>https://www.indeed.com/viewjob?jk=fc6dd2f1d6844211</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GCP Data Engineer – Remote</t>
+          <t>Senior AWS Agentic AI Engineer – Snowflake</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>YT Global Network</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Hadoop, Hive, Spark, PySpark</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b02a541e66f4c5b</t>
+          <t>https://www.indeed.com/viewjob?jk=c24d04fca23f04a4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Software Engineer - Digital Banking</t>
+          <t>Data Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acb73e15b88b41b2</t>
+          <t>https://www.indeed.com/viewjob?jk=0ab03e483c84aee8</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AWS DevOps Engineer (Hybrid)</t>
+          <t>Data Engineer 4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, Hive, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -939,59 +939,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ae1a526db03909</t>
+          <t>https://www.indeed.com/viewjob?jk=ac695015f6e52803</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior AI Ops / DevOps Engineer (FTE / Hybrid)</t>
+          <t>Senior Machine Learning Engineer, Fraud Risk Modeling</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6415d34be34565d8</t>
+          <t>https://www.indeed.com/viewjob?jk=0c1b0bc837735bcf</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -999,7 +999,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, RDS, Azure, Databricks, Spark, Scala, Snowflake</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1009,67 +1009,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac695015f6e52803</t>
+          <t>https://www.indeed.com/viewjob?jk=a88c40e681df4e1a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Erlanger, KY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a88c40e681df4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=f50c7dd606761e70</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Fraud Risk Modeling</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Howard Hughes Medical Institute</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, Snowflake, PostgreSQL, MongoDB</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1079,32 +1079,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1b0bc837735bcf</t>
+          <t>https://www.indeed.com/viewjob?jk=97c5e1818487b920</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>IT Analyst II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kroll Inc.</t>
+          <t>Texplorers Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Mechanicsville, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1114,24 +1114,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78b96535deace3b6</t>
+          <t>https://www.indeed.com/viewjob?jk=b652234b01407384</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Data Engineer (Platform)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Howard Hughes Medical Institute</t>
+          <t>Worth AI</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Spark</t>
+          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1149,24 +1149,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97c5e1818487b920</t>
+          <t>https://www.indeed.com/viewjob?jk=75ceb496aa16205b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer (Platform)</t>
+          <t>C,C++, Python, Golang Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Worth AI</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1174,34 +1174,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75ceb496aa16205b</t>
+          <t>https://www.indeed.com/viewjob?jk=3aaed4db41a0b1f5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>C++, Python, Golang Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1209,34 +1209,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e6a45e7ed84165b</t>
+          <t>https://www.indeed.com/viewjob?jk=4079e0cd8f01503b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Predictive Sales A.I.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1244,59 +1244,59 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Dask, Polars, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934be651d2822067</t>
+          <t>https://www.indeed.com/viewjob?jk=94a1a6eaf40c260e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lantern</t>
+          <t>Predictive Sales A.I.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Databricks, Unity Catalog, Scala, PostgreSQL, ELT, dbt, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, Dask, Polars, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2ab2b60d846cd6</t>
+          <t>https://www.indeed.com/viewjob?jk=4c03750cbc30f39f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1310,11 +1310,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1324,32 +1324,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aea92000540cf9d5</t>
+          <t>https://www.indeed.com/viewjob?jk=7e6a45e7ed84165b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Engineer, IT Machine Learning</t>
+          <t>Angular Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Oracle, ETL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1359,24 +1359,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab9e361c44f6f503</t>
+          <t>https://www.indeed.com/viewjob?jk=934be651d2822067</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Lantern</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>IAM, RDS, Azure, Databricks, Unity Catalog, Scala, PostgreSQL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1394,67 +1394,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aac1512204e679c4</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2ab2b60d846cd6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Developer (Loveland, CO)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NAC Architecture</t>
+          <t>Antech Diagnostics</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Loveland, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Kafka, Oracle, NoSQL, Data Modeling, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de63d204e832110a</t>
+          <t>https://www.indeed.com/viewjob?jk=12afaeb4d5194deb</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NAC Architecture</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spokane, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1464,32 +1464,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=876322e831ec8eca</t>
+          <t>https://www.indeed.com/viewjob?jk=aea92000540cf9d5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NAC Architecture</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1499,24 +1499,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c07ba22730cc31c</t>
+          <t>https://www.indeed.com/viewjob?jk=aac1512204e679c4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Platform Engineer/DevOp</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NAC Architecture</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1524,17 +1524,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d993410e2b916af</t>
+          <t>https://www.indeed.com/viewjob?jk=03c13abcae168f92</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>NAC Architecture</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1569,24 +1569,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b7784fe0428d5f</t>
+          <t>https://www.indeed.com/viewjob?jk=de63d204e832110a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GenAI Engineer / Forward Deployed Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NAC Architecture</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Spokane, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, PostgreSQL, DynamoDB</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1604,24 +1604,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073e98661976c07a</t>
+          <t>https://www.indeed.com/viewjob?jk=876322e831ec8eca</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ProMach</t>
+          <t>NAC Architecture</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1639,24 +1639,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66c9f802c8d368c6</t>
+          <t>https://www.indeed.com/viewjob?jk=7c07ba22730cc31c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Development Engineer- Product Reliability Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>NAC Architecture</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1674,19 +1674,19 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f35bd1de3b8b37e</t>
+          <t>https://www.indeed.com/viewjob?jk=0d993410e2b916af</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - Observability Platform</t>
+          <t>GenAI Engineer / Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1709,129 +1709,129 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26cf82ccf38514ed</t>
+          <t>https://www.indeed.com/viewjob?jk=073e98661976c07a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Analytics Engineer II, Marketing Technology - Remote</t>
+          <t>SDC WAMT Back End Engineer---Analyst---Dallas, Raleigh, San Antonio</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OneDigital</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Blob Storage, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=238a27c5210ae789</t>
+          <t>https://www.indeed.com/viewjob?jk=7c11d949a142a620</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer - Data Architecture &amp; Platform Engineering</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>News Corp</t>
+          <t>ProMach</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, ELT, dbt, Tableau</t>
+          <t>RDS, Databricks, Unity Catalog, Spark, Scala, Oracle, SQL Server, PostgreSQL, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=923379e0dc0b8dde</t>
+          <t>https://www.indeed.com/viewjob?jk=66c9f802c8d368c6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer-4</t>
+          <t>Software Development Engineer- Product Reliability Engineering</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Data Modeling, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7d0c3f29b8874fb</t>
+          <t>https://www.indeed.com/viewjob?jk=0f35bd1de3b8b37e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Credit Union of Texas</t>
+          <t>iSynergy Information Technologies</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Allen, TX, US USA</t>
+          <t>McKinney, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1839,42 +1839,42 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933f7b241bea8b88</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f610986642a7b2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Engineer II, Marketing Technology - Remote</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Easterseals Southern California</t>
+          <t>OneDigital</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Blob Storage, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1884,19 +1884,19 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07870ee9c10ac5c8</t>
+          <t>https://www.indeed.com/viewjob?jk=238a27c5210ae789</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Security Platform Engineer</t>
+          <t>Software Engineer - Data Architecture &amp; Platform Engineering</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Equinox</t>
+          <t>News Corp</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1905,11 +1905,11 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD, Maven, Terraform</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1919,67 +1919,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f48fee844cd0c55d</t>
+          <t>https://www.indeed.com/viewjob?jk=923379e0dc0b8dde</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Information Security Engineer</t>
+          <t>Data Engineer-4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>reveleer</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Databricks, GCP, MLOps, MLflow</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30bee6defc91ca2b</t>
+          <t>https://www.indeed.com/viewjob?jk=c7d0c3f29b8874fb</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>District Integration &amp; Support Engineer (Systems Engineer I) - 61161120</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>State of South Carolina</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Montgomery, AL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Talend, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1989,89 +1989,89 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d5ffc90f30b5ea7</t>
+          <t>https://www.indeed.com/viewjob?jk=221eb91487776685</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Devops Engineer</t>
+          <t>SDC WAMT Senior Backend Engineer---Senior-----Dallas, Raleigh, San Antonio</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be020efc616ae06a</t>
+          <t>https://www.indeed.com/viewjob?jk=e65c5560ca576a10</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DevSecOps Engineer</t>
+          <t>AI/ML Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Harris Computer</t>
+          <t>DFUSE TECHNOLOGIES</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Ai, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, ECS, Azure, Google Cloud Platform, GCP, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=274f51e93c4990cb</t>
+          <t>https://www.indeed.com/viewjob?jk=ab3ef12034fb6c8a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Backend</t>
+          <t>Sr. Information Security Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>reveleer</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2084,34 +2084,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, ECS, IAM, RDS, Azure, Databricks, GCP, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff1e374638f96eca</t>
+          <t>https://www.indeed.com/viewjob?jk=30bee6defc91ca2b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Visualization Engineer</t>
+          <t>District Integration &amp; Support Engineer (Systems Engineer I) - 61161120</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tempus</t>
+          <t>State of South Carolina</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2119,42 +2119,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, dbt, Power BI</t>
+          <t>Redshift, RDS, Azure, BigQuery, Scala, Snowflake, Talend, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5131e2f85865e971</t>
+          <t>https://www.indeed.com/viewjob?jk=0d5ffc90f30b5ea7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Professional Services Engineer</t>
+          <t>Senior Devops Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Dataflow, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2164,59 +2164,59 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0f07433764ff47c</t>
+          <t>https://www.indeed.com/viewjob?jk=be020efc616ae06a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Senior Security Platform Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Blue Shield of California</t>
+          <t>Equinox</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, ECS, IAM, RDS, Azure, GCP, Scala, CI/CD, Maven, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8456a013be9abe6d</t>
+          <t>https://www.indeed.com/viewjob?jk=f48fee844cd0c55d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer - Associate</t>
+          <t>Service Delivery Center, Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Richmond</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Snowflake, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2234,24 +2234,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47786603c2f15c79</t>
+          <t>https://www.indeed.com/viewjob?jk=16371cbe9a6f6a94</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer- Enterprise Platforms</t>
+          <t>Professional Services Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2259,34 +2259,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, GCP, Dataflow, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1c6131bc8b3c29</t>
+          <t>https://www.indeed.com/viewjob?jk=e0f07433764ff47c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Architect - Data &amp; Analytics COE</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>United Nations Federal Credit Union</t>
+          <t>Blue Shield of California</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2304,24 +2304,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4543534bd5d880f4</t>
+          <t>https://www.indeed.com/viewjob?jk=8456a013be9abe6d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2027 Capital Markets, Quantitative Technology Services Summer, Raleigh</t>
+          <t>AI Solutions Engineer - Associate</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RBC</t>
+          <t>Federal Reserve Bank of Richmond</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Kafka, NoSQL, ETL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2339,24 +2339,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea97b81f8a8fbea5</t>
+          <t>https://www.indeed.com/viewjob?jk=47786603c2f15c79</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer Analyst</t>
+          <t>Senior Software Engineer- Enterprise Platforms</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Fannie Mae</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2364,34 +2364,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15d208d296c27320</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1c6131bc8b3c29</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Architect - Data &amp; Analytics COE</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>United Nations Federal Credit Union</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Long Island City, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2409,24 +2409,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57923c372a91491</t>
+          <t>https://www.indeed.com/viewjob?jk=4543534bd5d880f4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr AI/Data Science Engineer</t>
+          <t>2027 Capital Markets, Quantitative Technology Services Summer, Raleigh</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MiniMed</t>
+          <t>RBC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Northridge, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, ELT, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Kafka, NoSQL, ETL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2444,24 +2444,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96bdba5085886da3</t>
+          <t>https://www.indeed.com/viewjob?jk=ea97b81f8a8fbea5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer III - Backend</t>
+          <t>Full Stack Software Engineer Analyst</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2479,24 +2479,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bfe9ad476bd328d</t>
+          <t>https://www.indeed.com/viewjob?jk=15d208d296c27320</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tinder</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2514,24 +2514,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd1157f032a62ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d57923c372a91491</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Software Engineer III, Backend</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Tinder</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, ECS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2549,24 +2549,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06a412cb9f758689</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd1157f032a62ba</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer III, Backend</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Meetic</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2584,24 +2584,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcdac1dc01d8884d</t>
+          <t>https://www.indeed.com/viewjob?jk=06a412cb9f758689</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III, Backend</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Meetic</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, ETL, Talend, CI/CD</t>
+          <t>AWS, ECS, Azure, Google Cloud Platform, Spark, Scala, Kafka, DynamoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d32bc60368c3a448</t>
+          <t>https://www.indeed.com/viewjob?jk=bcdac1dc01d8884d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Wireless Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DMI</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Crownsville, MD, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, ETL, Talend, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2654,24 +2654,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64fcbfb44e8f3307</t>
+          <t>https://www.indeed.com/viewjob?jk=d32bc60368c3a448</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr DevOps Engineer</t>
+          <t>Wireless Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nuuly</t>
+          <t>DMI</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Crownsville, MD, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Zookeeper, Scala, Kafka, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2689,24 +2689,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c18e77b373c042e</t>
+          <t>https://www.indeed.com/viewjob?jk=64fcbfb44e8f3307</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>IT Analyst III - Cloud Automation and Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>North South Consulting Group</t>
+          <t>State of Utah</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Taylorsville, UT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2714,34 +2714,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33388762be2726a2</t>
+          <t>https://www.indeed.com/viewjob?jk=c9184edf09372f2a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Rezilient Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2749,34 +2749,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31614612c22a3bf8</t>
+          <t>https://www.indeed.com/viewjob?jk=2ba5d9d223a8fba0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer</t>
+          <t>Senior Data Engineer (Snowflake, MySQL, Python)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Covington, KY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2784,34 +2784,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, MySQL, ETL, ELT, Tableau, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d42345033b70a0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=da43c24abcf89178</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer – Azure Practitioner</t>
+          <t>Sr DevOps Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>KCI Technologies</t>
+          <t>Nuuly</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Zookeeper, Scala, Kafka, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2829,24 +2829,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d231129436df5d79</t>
+          <t>https://www.indeed.com/viewjob?jk=7c18e77b373c042e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Analytics Engineer, Associate</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TPG</t>
+          <t>North South Consulting Group</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2854,34 +2854,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6e6546ed6025d10</t>
+          <t>https://www.indeed.com/viewjob?jk=33388762be2726a2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Erwin Data Modeler</t>
+          <t>Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tekcogno</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Scala, Snowflake, Oracle, SQL Server, MongoDB, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2899,24 +2899,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89810a7e8484847e</t>
+          <t>https://www.indeed.com/viewjob?jk=d42345033b70a0ad</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>DBT/Python/Airflow Developer</t>
+          <t>Site Reliability Engineer III – AI-Centric Application Performance &amp; FinOps</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2924,34 +2924,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=551ec71ed16874e7</t>
+          <t>https://www.indeed.com/viewjob?jk=acc60f244ee03aef</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full-Stack Software Engineer – Azure Practitioner</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>World Emblem International</t>
+          <t>KCI Technologies</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, SQL Server, Dimensional Modeling, Star Schema, Dimension Tables, ETL, ELT</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2969,24 +2969,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb03498bcaeb2d4</t>
+          <t>https://www.indeed.com/viewjob?jk=d231129436df5d79</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Analytics Engineer, Associate</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>World Emblem International</t>
+          <t>TPG</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -2994,34 +2994,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, SQL Server, Dimensional Modeling, Star Schema, Dimension Tables, ETL, ELT</t>
+          <t>AWS, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, SQL Server, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0020052b83f9ef57</t>
+          <t>https://www.indeed.com/viewjob?jk=a6e6546ed6025d10</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>DBT/Python/Airflow Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>World Emblem International</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Norcross, GA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3029,17 +3029,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Dataflow, SQL Server, Dimensional Modeling, Star Schema, Dimension Tables, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, Snowflake Schema, ETL, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=767b9e8e13621baf</t>
+          <t>https://www.indeed.com/viewjob?jk=551ec71ed16874e7</t>
         </is>
       </c>
     </row>
@@ -3151,17 +3151,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Clinician-Developer: Cloud &amp; Integrations</t>
+          <t>Machine Learning Engineer - CTO innovations</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Charleston Children’s Therapy Center</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, Docker, AKS</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Snowflake, ETL, ELT, Airflow, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3179,24 +3179,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf03acdee6bfb411</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb6bdbcc89b8901</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer (In Person)</t>
+          <t>Clinician-Developer: Cloud &amp; Integrations</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Westchester Medical Center Health Network</t>
+          <t>Charleston Children’s Therapy Center</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Valhalla, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, EMR, Lambda, S3, IAM, RDS, PostgreSQL, CI/CD, Docker, AKS</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3214,24 +3214,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6442e1547a870e80</t>
+          <t>https://www.indeed.com/viewjob?jk=bf03acdee6bfb411</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analytics Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Westchester Medical Center Health Network</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Aventura, FL, US USA</t>
+          <t>Valhalla, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3239,34 +3239,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, SQL Server, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Snowflake, SQL Server, Data Modeling, ELT, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c493980a69f74556</t>
+          <t>https://www.indeed.com/viewjob?jk=6442e1547a870e80</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Aventura, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Blob Storage, Unity Catalog, Scala, SQL Server, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3284,24 +3284,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b77e2e5fec6bdd9d</t>
+          <t>https://www.indeed.com/viewjob?jk=c493980a69f74556</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Enterprise Data Engineer</t>
+          <t>Senior Software Engineer, Platform Engineering</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Shelter Insurance</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Columbia, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Git</t>
+          <t>AWS, IAM, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e4f2633f539c6b2</t>
+          <t>https://www.indeed.com/viewjob?jk=b77e2e5fec6bdd9d</t>
         </is>
       </c>
     </row>
@@ -3361,17 +3361,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Innovate Tech IT LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sheridan, WY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3379,34 +3379,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e9b73c6f8692132</t>
+          <t>https://www.indeed.com/viewjob?jk=389bda3afea947e0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - NC - Mandarin Speaking (Full-time, Exempt)</t>
+          <t>Solutions Architect - Digital Native Business (Fintech)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3414,34 +3414,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Git, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d98c4c1704c4e527</t>
+          <t>https://www.indeed.com/viewjob?jk=a95aea0382d2db66</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - CA - Mandarin Speaking</t>
+          <t>Senior Data Quality Analyst</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Breakthru Beverage Group</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>City of Industry, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3449,34 +3449,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, dbt, Airflow, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc57e420a23e41b3</t>
+          <t>https://www.indeed.com/viewjob?jk=83f52a8d71cbe4d7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DevOps/SRE Engineer - Bilingual Mandarin Required</t>
+          <t>Senior Data Quality Analyst</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cwill</t>
+          <t>Breakthru Beverage Group</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3484,34 +3484,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, CI/CD, Jenkins, CodeBuild, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, dbt, Airflow, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c1901ef9cd7bdba</t>
+          <t>https://www.indeed.com/viewjob?jk=064892ad293de829</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Senior Data Quality Analyst</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Novacis Digital</t>
+          <t>Breakthru Beverage Group</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Linthicum, MD, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3519,17 +3519,122 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>IAM, Azure, Data Factory, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, ETL, dbt, Airflow, Python, SQL, Scala</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddb729860cdaaf66</t>
+          <t>https://www.indeed.com/viewjob?jk=23995c14ef6d4f73</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Data Quality Analyst</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Breakthru Beverage Group</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, ETL, dbt, Airflow, Python, SQL, Scala</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=482a123ad569f8d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Data Quality Analyst</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Breakthru Beverage Group</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, ETL, dbt, Airflow, Python, SQL, Scala</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de8de9417533fb28</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Innovate Tech IT LLC</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Sheridan, WY, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, PostgreSQL, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e9b73c6f8692132</t>
         </is>
       </c>
     </row>
